--- a/InputData/elec/EIaE/Elec Imports and Exports.xlsx
+++ b/InputData/elec/EIaE/Elec Imports and Exports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/EIaE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E879A49-B858-9E45-A5D8-B3DC96B6CEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DB8997-4C91-D74C-9A62-0FF19485D117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -231,7 +231,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +298,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -349,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -377,6 +384,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1918,7 +1926,7 @@
         <v>2018</v>
       </c>
       <c r="D25">
-        <f t="shared" ref="D25:BF25" si="1">C25+1</f>
+        <f t="shared" ref="D25:BC25" si="1">C25+1</f>
         <v>2019</v>
       </c>
       <c r="E25">
@@ -3461,14 +3469,14 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -3568,8 +3576,68 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="15">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="15">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="15">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="15">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="15">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="15">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="15">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="15">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="15">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="15">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="15">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="15">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="15">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="15">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="15">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="15">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="15">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="15">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="15">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="15">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3669,8 +3737,68 @@
       <c r="AG2">
         <v>0</v>
       </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1">
+    <row r="3" spans="1:53" ht="14.25" customHeight="1">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -3770,8 +3898,68 @@
       <c r="AG3">
         <v>0</v>
       </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1">
+    <row r="4" spans="1:53" ht="14.25" customHeight="1">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -3871,8 +4059,68 @@
       <c r="AG4">
         <v>0</v>
       </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1">
+    <row r="5" spans="1:53" ht="14.25" customHeight="1">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -4004,8 +4252,88 @@
         <f>'Electricity import'!AI26*1000</f>
         <v>10653995.605055023</v>
       </c>
+      <c r="AH5">
+        <f>'Electricity import'!AJ26*1000</f>
+        <v>10942861.543460023</v>
+      </c>
+      <c r="AI5">
+        <f>'Electricity import'!AK26*1000</f>
+        <v>11231727.481865024</v>
+      </c>
+      <c r="AJ5">
+        <f>'Electricity import'!AL26*1000</f>
+        <v>11520593.420270024</v>
+      </c>
+      <c r="AK5">
+        <f>'Electricity import'!AM26*1000</f>
+        <v>11809459.358675025</v>
+      </c>
+      <c r="AL5">
+        <f>'Electricity import'!AN26*1000</f>
+        <v>12098325.297080025</v>
+      </c>
+      <c r="AM5">
+        <f>'Electricity import'!AO26*1000</f>
+        <v>12387191.235485027</v>
+      </c>
+      <c r="AN5">
+        <f>'Electricity import'!AP26*1000</f>
+        <v>12676057.173890026</v>
+      </c>
+      <c r="AO5">
+        <f>'Electricity import'!AQ26*1000</f>
+        <v>12964923.112295028</v>
+      </c>
+      <c r="AP5">
+        <f>'Electricity import'!AR26*1000</f>
+        <v>13253789.050700027</v>
+      </c>
+      <c r="AQ5">
+        <f>'Electricity import'!AS26*1000</f>
+        <v>13542654.989105029</v>
+      </c>
+      <c r="AR5">
+        <f>'Electricity import'!AT26*1000</f>
+        <v>13831520.927510031</v>
+      </c>
+      <c r="AS5">
+        <f>'Electricity import'!AU26*1000</f>
+        <v>14120386.86591503</v>
+      </c>
+      <c r="AT5">
+        <f>'Electricity import'!AV26*1000</f>
+        <v>14409252.804320032</v>
+      </c>
+      <c r="AU5">
+        <f>'Electricity import'!AW26*1000</f>
+        <v>14698118.742725031</v>
+      </c>
+      <c r="AV5">
+        <f>'Electricity import'!AX26*1000</f>
+        <v>14986984.681130033</v>
+      </c>
+      <c r="AW5">
+        <f>'Electricity import'!AY26*1000</f>
+        <v>15275850.619535033</v>
+      </c>
+      <c r="AX5">
+        <f>'Electricity import'!AZ26*1000</f>
+        <v>15564716.557940036</v>
+      </c>
+      <c r="AY5">
+        <f>'Electricity import'!BA26*1000</f>
+        <v>15853582.496345036</v>
+      </c>
+      <c r="AZ5">
+        <f>'Electricity import'!BB26*1000</f>
+        <v>16142448.434750037</v>
+      </c>
+      <c r="BA5">
+        <f>'Electricity import'!BC26*1000</f>
+        <v>16431314.373155037</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1">
+    <row r="6" spans="1:53" ht="14.25" customHeight="1">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -4105,8 +4433,68 @@
       <c r="AG6">
         <v>0</v>
       </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1">
+    <row r="7" spans="1:53" ht="14.25" customHeight="1">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -4206,8 +4594,68 @@
       <c r="AG7">
         <v>0</v>
       </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1">
+    <row r="8" spans="1:53" ht="14.25" customHeight="1">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -4307,8 +4755,68 @@
       <c r="AG8">
         <v>0</v>
       </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1">
+    <row r="9" spans="1:53" ht="14.25" customHeight="1">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -4408,8 +4916,68 @@
       <c r="AG9">
         <v>0</v>
       </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1">
+    <row r="10" spans="1:53" ht="14.25" customHeight="1">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -4509,8 +5077,68 @@
       <c r="AG10">
         <v>0</v>
       </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1">
+    <row r="11" spans="1:53" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -4610,8 +5238,68 @@
       <c r="AG11">
         <v>0</v>
       </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1">
+    <row r="12" spans="1:53" ht="14.25" customHeight="1">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -4711,8 +5399,68 @@
       <c r="AG12">
         <v>0</v>
       </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1">
+    <row r="13" spans="1:53" ht="14.25" customHeight="1">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -4812,8 +5560,68 @@
       <c r="AG13">
         <v>0</v>
       </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1">
+    <row r="14" spans="1:53" ht="14.25" customHeight="1">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4913,8 +5721,68 @@
       <c r="AG14">
         <v>0</v>
       </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1">
+    <row r="15" spans="1:53" ht="14.25" customHeight="1">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -5014,8 +5882,68 @@
       <c r="AG15">
         <v>0</v>
       </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1">
+    <row r="16" spans="1:53" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -5115,8 +6043,68 @@
       <c r="AG16">
         <v>0</v>
       </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1">
+    <row r="17" spans="1:53" ht="14.25" customHeight="1">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -5216,22 +6204,82 @@
       <c r="AG17">
         <v>0</v>
       </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:53" ht="14.25" customHeight="1"/>
     <row r="33" customFormat="1" ht="14.25" customHeight="1"/>
     <row r="34" customFormat="1" ht="14.25" customHeight="1"/>
     <row r="35" customFormat="1" ht="14.25" customHeight="1"/>
@@ -6211,14 +7259,14 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -6318,8 +7366,68 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="15">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="15">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="15">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="15">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="15">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="15">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="15">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="15">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="15">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="15">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="15">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="15">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="15">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="15">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="15">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="15">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="15">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="15">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="15">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="15">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -6419,21 +7527,81 @@
       <c r="AG2">
         <v>0</v>
       </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:53" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:53" ht="14.25" customHeight="1"/>
     <row r="17" customFormat="1" ht="14.25" customHeight="1"/>
     <row r="18" customFormat="1" ht="14.25" customHeight="1"/>
     <row r="19" customFormat="1" ht="14.25" customHeight="1"/>
@@ -7430,13 +8598,13 @@
     <tabColor rgb="FF0070C0"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:53">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -7536,8 +8704,68 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="15">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="15">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="15">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="15">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="15">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="15">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="15">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="15">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="15">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="15">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="15">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="15">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="15">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="15">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="15">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="15">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="15">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="15">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="15">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="15">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:53">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -7666,6 +8894,86 @@
         <v>183.28363438</v>
       </c>
       <c r="AG2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AH2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AI2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AJ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AK2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AL2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AM2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AN2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AO2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AP2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AQ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AR2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AS2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AT2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AU2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AV2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AW2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AX2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AY2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AZ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="BA2">
         <f>'Electricity price'!$G$32</f>
         <v>183.28363438</v>
       </c>
@@ -7681,13 +8989,13 @@
     <tabColor rgb="FF0070C0"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:53">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -7787,8 +9095,68 @@
       <c r="AG1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="15">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="15">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="15">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="15">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="15">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="15">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="15">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="15">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="15">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="15">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="15">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="15">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="15">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="15">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="15">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="15">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="15">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="15">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="15">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="15">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:53">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -7917,6 +9285,86 @@
         <v>183.28363438</v>
       </c>
       <c r="AG2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AH2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AI2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AJ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AK2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AL2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AM2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AN2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AO2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AP2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AQ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AR2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AS2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AT2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AU2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AV2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AW2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AX2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AY2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="AZ2">
+        <f>'Electricity price'!$G$32</f>
+        <v>183.28363438</v>
+      </c>
+      <c r="BA2">
         <f>'Electricity price'!$G$32</f>
         <v>183.28363438</v>
       </c>
